--- a/Result/profitability/6292.xlsx
+++ b/Result/profitability/6292.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.44375</v>
+        <v>0.76375</v>
       </c>
       <c r="N2" t="n">
-        <v>35.03</v>
+        <v>36.29</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44875</v>
+        <v>0.7662500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>34.41</v>
+        <v>35.50625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.47375</v>
+        <v>0.7775000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>33.84875</v>
+        <v>34.84875</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.16</v>
+        <v>0.5537500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>33.0925</v>
+        <v>33.88375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25</v>
+        <v>0.49875</v>
       </c>
       <c r="N6" t="n">
-        <v>32.32375</v>
+        <v>33.6275</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.215</v>
+        <v>0.41375</v>
       </c>
       <c r="N7" t="n">
-        <v>32.48125</v>
+        <v>33.42625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1475</v>
+        <v>0.405</v>
       </c>
       <c r="N8" t="n">
-        <v>32.90375</v>
+        <v>34.2625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6292</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>308</v>
+      </c>
+      <c r="D75" t="n">
+        <v>173</v>
+      </c>
+      <c r="E75" t="n">
+        <v>136</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>61</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>85</v>
+      </c>
+      <c r="J75" t="n">
+        <v>146</v>
+      </c>
+      <c r="K75" t="n">
+        <v>130</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.821917808219178</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3278045838359471</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.329999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1679045092838196</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
